--- a/data/trans_dic/P22$notiene-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P22$notiene-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene Seguro Sanitario</t>
+          <t>Población que no tiene seguro médico (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,47</t>
+          <t>0,0; 4,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 1,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,22</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,42</t>
+          <t>0,0; 0,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,17</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,73</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,21</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,22</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,94</t>
+          <t>0,0; 4,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,55</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1557,52 +1557,52 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,69</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,41</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,68</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,31</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,3</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,3</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,41</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,84</t>
-        </is>
-      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,38</t>
+          <t>0,0; 0,4</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,01; 0,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,49</t>
+          <t>0,27; 1,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,45</t>
+          <t>0,0; 0,47</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,4</t>
+          <t>0,0; 0,42</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,53</t>
+          <t>0,0; 0,46</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,82</t>
+          <t>0,17; 0,79</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,46</t>
+          <t>0,05; 0,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,29</t>
+          <t>0,04; 0,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,45</t>
+          <t>0,07; 0,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>0,03; 0,25</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,19</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,18</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t>0,02; 0,25</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,22</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,19</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>0,02; 0,25</t>
-        </is>
-      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,34</t>
+          <t>0,07; 0,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,26</t>
+          <t>0,05; 0,25</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,18</t>
+          <t>0,02; 0,17</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,27</t>
+          <t>0,07; 0,29</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,23</t>
+          <t>0,07; 0,22</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene Seguro Sanitario</t>
+          <t>Población que no tiene seguro médico (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 12160</t>
+          <t>0; 11425</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 8675</t>
+          <t>0; 9576</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2112</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1801</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2035</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2145</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6837</t>
+          <t>0; 5666</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1032</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 11677</t>
+          <t>0; 12762</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 8477</t>
+          <t>0; 7401</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6047</t>
+          <t>0; 7289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 1327</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2031</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2052</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2027</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2598</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1935</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2091</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5445</t>
+          <t>0; 5917</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1377</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1984</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2074</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4347</t>
+          <t>0; 5438</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 1804</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6250</t>
+          <t>0; 5216</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1944</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1820</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1681</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1916</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2058</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1939</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1248</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4784</t>
+          <t>0; 5199</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 2005</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1883</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 1424</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1896</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2081</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 9322</t>
+          <t>0; 8867</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2047</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1853</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2071</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 1522</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1877</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 8812</t>
+          <t>0; 9603</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 1697</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1885</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2071</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 8327</t>
+          <t>0; 9927</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1225</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2002</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6054</t>
+          <t>0; 6009</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5178</t>
+          <t>0; 4686</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2192</t>
+          <t>0; 2090</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1948</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6493</t>
+          <t>0; 6039</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 8977</t>
+          <t>0; 8370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2530</t>
+          <t>0; 2123</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1947</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1942</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 1391</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1970</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1991</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 1985</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 1071</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1963</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 2003</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 1969</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 1216</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 7845</t>
+          <t>0; 8778</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2056</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5598</t>
+          <t>0; 6327</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4247</t>
+          <t>0; 4278</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1970</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2091</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2050</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3512</t>
+          <t>0; 3461</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 10450</t>
+          <t>0; 8542</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 2076</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 5248</t>
+          <t>0; 5291</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0; 5642</t>
+          <t>0; 5847</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 1937</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 7649</t>
+          <t>0; 5894</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 8139</t>
+          <t>0; 7922</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 6696</t>
+          <t>128; 7517</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 7131</t>
+          <t>0; 7366</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 2087</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 2098</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2023; 10695</t>
+          <t>1937; 10319</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 6835</t>
+          <t>0; 7152</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 6469</t>
+          <t>0; 6767</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 8494</t>
+          <t>0; 7365</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2596; 13410</t>
+          <t>2782; 12931</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1652; 14932</t>
+          <t>1659; 15454</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1210; 9909</t>
+          <t>1211; 11066</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2268; 15345</t>
+          <t>2281; 14424</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>766; 8713</t>
+          <t>893; 8496</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0; 7585</t>
+          <t>0; 6450</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0; 6591</t>
+          <t>0; 6466</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>849; 8843</t>
+          <t>850; 8879</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2888; 12462</t>
+          <t>2627; 11475</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3377; 17536</t>
+          <t>3139; 16800</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1234; 12286</t>
+          <t>1230; 12221</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4332; 18989</t>
+          <t>5010; 19820</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4762; 16226</t>
+          <t>4660; 15786</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$notiene-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P22$notiene-Provincia-trans_dic.xlsx
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,2</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,53</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,55</t>
+          <t>0,0; 0,59</t>
         </is>
       </c>
     </row>
@@ -1504,47 +1504,47 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,12%</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,41</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,39</t>
+          <t>0,0; 0,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,4</t>
+          <t>0,0; 0,37</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -1702,22 +1702,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,81</t>
+          <t>0,11; 1,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1732,27 +1732,27 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,44</t>
+          <t>0,26; 1,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,47</t>
+          <t>0,0; 0,46</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,42</t>
+          <t>0,0; 0,4</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,53</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,79</t>
+          <t>0,26; 1,12</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,27 +1804,27 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,47</t>
+          <t>0,05; 0,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,32</t>
+          <t>0,04; 0,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,43</t>
+          <t>0,07; 0,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,25</t>
+          <t>0,03; 0,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,21</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,19</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,18</t>
-        </is>
-      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,25</t>
+          <t>0,02; 0,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,31</t>
+          <t>0,09; 0,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,25</t>
+          <t>0,04; 0,26</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,17</t>
+          <t>0,02; 0,18</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,29</t>
+          <t>0,06; 0,26</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,22</t>
+          <t>0,09; 0,29</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 11425</t>
+          <t>0; 11048</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 9576</t>
+          <t>0; 7409</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5666</t>
+          <t>0; 5516</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,17 +2249,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 12762</t>
+          <t>0; 11541</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 7401</t>
+          <t>0; 7389</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 7289</t>
+          <t>0; 6639</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5917</t>
+          <t>0; 4387</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5438</t>
+          <t>0; 6357</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5216</t>
+          <t>0; 6291</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5199</t>
+          <t>0; 5184</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 8867</t>
+          <t>0; 9941</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 9603</t>
+          <t>0; 10615</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>441</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>441</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 9927</t>
+          <t>0; 8616</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3066,17 +3066,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6009</t>
+          <t>0; 5886</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4686</t>
+          <t>0; 5145</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2090</t>
+          <t>0; 2710</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -3086,17 +3086,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6039</t>
+          <t>0; 5709</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 8370</t>
+          <t>0; 10541</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2123</t>
+          <t>0; 2555</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>708</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1761</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 8778</t>
+          <t>0; 8760</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 6327</t>
+          <t>0; 5264</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4278</t>
+          <t>0; 5900</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3461</t>
+          <t>0; 4755</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 8542</t>
+          <t>0; 8805</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 5291</t>
+          <t>0; 5293</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0; 5847</t>
+          <t>0; 5463</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>9375</t>
         </is>
       </c>
     </row>
@@ -3670,22 +3670,22 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 5894</t>
+          <t>0; 6389</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 7922</t>
+          <t>0; 8972</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>128; 7517</t>
+          <t>896; 11094</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 7366</t>
+          <t>0; 7150</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3700,27 +3700,27 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1937; 10319</t>
+          <t>2173; 11214</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 7152</t>
+          <t>0; 7014</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 6767</t>
+          <t>0; 6334</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 7365</t>
+          <t>0; 8552</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2782; 12931</t>
+          <t>4259; 18299</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>8863</t>
+          <t>11577</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1659; 15454</t>
+          <t>1656; 15998</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1211; 11066</t>
+          <t>1211; 9987</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2281; 14424</t>
+          <t>2448; 15129</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>893; 8496</t>
+          <t>1142; 12727</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0; 6450</t>
+          <t>0; 7014</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0; 6466</t>
+          <t>0; 6855</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>850; 8879</t>
+          <t>849; 9559</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2627; 11475</t>
+          <t>3324; 13001</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3139; 16800</t>
+          <t>2864; 17250</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1230; 12221</t>
+          <t>1266; 12256</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5010; 19820</t>
+          <t>4345; 17970</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4660; 15786</t>
+          <t>6248; 20926</t>
         </is>
       </c>
     </row>
